--- a/Druckerliste_CARI_export.xlsx
+++ b/Druckerliste_CARI_export.xlsx
@@ -48573,11 +48573,11 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_Ersatz</t>
+          <t>OB-SCH-Zulassung_1</t>
         </is>
       </c>
       <c r="C871" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -48629,11 +48629,11 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_Ersatz</t>
+          <t>OB-SCH-Zulassung_1</t>
         </is>
       </c>
       <c r="C872" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -48685,11 +48685,11 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_Ersatz</t>
+          <t>OB-SCH-Zulassung_1</t>
         </is>
       </c>
       <c r="C873" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -48741,11 +48741,11 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_Ersatz</t>
+          <t>OB-SCH-Zulassung_1</t>
         </is>
       </c>
       <c r="C874" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -48797,11 +48797,11 @@
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_Ersatz</t>
+          <t>OB-SCH-Zulassung_1</t>
         </is>
       </c>
       <c r="C875" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -48853,11 +48853,11 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_Ersatz</t>
+          <t>OB-SCH-Zulassung_1</t>
         </is>
       </c>
       <c r="C876" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -48909,11 +48909,11 @@
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_KUN</t>
+          <t>OB-SCH-Zulassung_2</t>
         </is>
       </c>
       <c r="C877" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -48965,11 +48965,11 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_KUN</t>
+          <t>OB-SCH-Zulassung_2</t>
         </is>
       </c>
       <c r="C878" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -49021,11 +49021,11 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_KUN</t>
+          <t>OB-SCH-Zulassung_2</t>
         </is>
       </c>
       <c r="C879" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -49077,11 +49077,11 @@
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_KUN</t>
+          <t>OB-SCH-Zulassung_2</t>
         </is>
       </c>
       <c r="C880" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -49133,15 +49133,15 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_KUN</t>
+          <t>OB-SCH-Zulassung_2</t>
         </is>
       </c>
       <c r="C881" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
-          <t>PSTVA5732</t>
+          <t>PSTVA5731</t>
         </is>
       </c>
       <c r="E881" t="inlineStr">
@@ -49189,15 +49189,15 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_KUN</t>
+          <t>OB-SCH-Zulassung_2</t>
         </is>
       </c>
       <c r="C882" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
-          <t>PSTVA5732</t>
+          <t>PSTVA5731</t>
         </is>
       </c>
       <c r="E882" t="inlineStr">
@@ -49245,11 +49245,11 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_KUV</t>
+          <t>OB-SCH-Zulassung_3</t>
         </is>
       </c>
       <c r="C883" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -49301,11 +49301,11 @@
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_KUV</t>
+          <t>OB-SCH-Zulassung_3</t>
         </is>
       </c>
       <c r="C884" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -49357,11 +49357,11 @@
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_KUV</t>
+          <t>OB-SCH-Zulassung_3</t>
         </is>
       </c>
       <c r="C885" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -49413,11 +49413,11 @@
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_KUV</t>
+          <t>OB-SCH-Zulassung_3</t>
         </is>
       </c>
       <c r="C886" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -49469,15 +49469,15 @@
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_KUV</t>
+          <t>OB-SCH-Zulassung_3</t>
         </is>
       </c>
       <c r="C887" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
-          <t>PSTVA5731</t>
+          <t>PSTVA5732</t>
         </is>
       </c>
       <c r="E887" t="inlineStr">
@@ -49525,15 +49525,15 @@
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_KUV</t>
+          <t>OB-SCH-Zulassung_3</t>
         </is>
       </c>
       <c r="C888" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
-          <t>PSTVA5731</t>
+          <t>PSTVA5732</t>
         </is>
       </c>
       <c r="E888" t="inlineStr">
@@ -49581,11 +49581,11 @@
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_MAM</t>
+          <t>OB-SCH-Zulassung_Ersatz</t>
         </is>
       </c>
       <c r="C889" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -49637,11 +49637,11 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_MAM</t>
+          <t>OB-SCH-Zulassung_Ersatz</t>
         </is>
       </c>
       <c r="C890" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -49693,11 +49693,11 @@
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_MAM</t>
+          <t>OB-SCH-Zulassung_Ersatz</t>
         </is>
       </c>
       <c r="C891" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -49749,11 +49749,11 @@
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_MAM</t>
+          <t>OB-SCH-Zulassung_Ersatz</t>
         </is>
       </c>
       <c r="C892" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -49805,11 +49805,11 @@
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_MAM</t>
+          <t>OB-SCH-Zulassung_Ersatz</t>
         </is>
       </c>
       <c r="C893" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -49861,11 +49861,11 @@
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_MAM</t>
+          <t>OB-SCH-Zulassung_Ersatz</t>
         </is>
       </c>
       <c r="C894" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -70204,26 +70204,10 @@
           <t>DE001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>A4</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Adressetikette</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>A4 -&gt; Match Page Size Landscape Manual Scaling 100% Origin at Center</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -70231,21 +70215,9 @@
           <t>DP_ACC</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Kontrollfahrt Bewilligung</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -70254,21 +70226,9 @@
           <t>DP_ATHN</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Bewilligungskarte Schifffahrt</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -70277,21 +70237,9 @@
           <t>DP_CGAR</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Anhang zum Fahrzeugausweis</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
@@ -70300,21 +70248,9 @@
           <t>DP_CGAV</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Rückseite Anhang zum Fahrzeugausweis</t>
-        </is>
-      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -70323,21 +70259,9 @@
           <t>DP_CGB</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Schiffsausweis</t>
-        </is>
-      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -70346,21 +70270,9 @@
           <t>DP_CGC</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Fahrzeugausweis kollektiv</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -70369,21 +70281,9 @@
           <t>DP_CGJ</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Tagesausweis</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -70392,21 +70292,9 @@
           <t>DP_CGN</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Fahrzeugausweis</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -70415,21 +70303,9 @@
           <t>DP_CGR</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Ersatzfahrzeugausweis</t>
-        </is>
-      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
@@ -70438,21 +70314,9 @@
           <t>DP_CGT</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Fahrzeugausweis befristet</t>
-        </is>
-      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -70461,21 +70325,9 @@
           <t>DP_CSH</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Behindertenparkkarte</t>
-        </is>
-      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -70484,21 +70336,9 @@
           <t>DP_CY</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Fahrzeugausweis MOFA</t>
-        </is>
-      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -70507,21 +70347,9 @@
           <t>DP_DC</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Entbindung der Gurtentragpflicht</t>
-        </is>
-      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
@@ -70530,21 +70358,9 @@
           <t>DP_PCBI</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Internationaler Schiffsführerausweis</t>
-        </is>
-      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -70553,21 +70369,9 @@
           <t>DP_PCBIA</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Internationaler Schiffsführerausweis Rückseite</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -70576,26 +70380,10 @@
           <t>DP_PCI</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>A4</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>CARi_DP_PCI</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Internationaler Führerausweis</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>A4 -&gt; CARi-DP-PCI 148 x 311 Landscape, Manual Scaling 100% Origin at Center</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -70603,21 +70391,9 @@
           <t>DP_PCN</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Führerausweis Schiff</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -70626,21 +70402,9 @@
           <t>DP_PE</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Führerausweis Lerner</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
@@ -70649,26 +70413,10 @@
           <t>FA030</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>A4</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Versandetikette Fahrzeug</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>A4 -&gt; Match Page Size Landscape Manual Scaling 100% Origin at Center</t>
-        </is>
-      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -70676,21 +70424,9 @@
           <t>FA031</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>A4</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>A4</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Internationale Versicherungskarte (Grüne Karte)</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
@@ -70701,11 +70437,7 @@
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Inspectdokument</t>
-        </is>
-      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
@@ -70716,11 +70448,7 @@
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Drucker für automatischer Druck des LF</t>
-        </is>
-      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
     </row>
   </sheetData>

--- a/Druckerliste_CARI_export.xlsx
+++ b/Druckerliste_CARI_export.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Druckerliste" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Forms" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Druckerliste" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forms" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -48573,11 +48573,11 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_Ersatz</t>
+          <t>OB-SCH-Zulassung_1</t>
         </is>
       </c>
       <c r="C871" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -48629,11 +48629,11 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_Ersatz</t>
+          <t>OB-SCH-Zulassung_1</t>
         </is>
       </c>
       <c r="C872" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -48685,11 +48685,11 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_Ersatz</t>
+          <t>OB-SCH-Zulassung_1</t>
         </is>
       </c>
       <c r="C873" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -48741,11 +48741,11 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_Ersatz</t>
+          <t>OB-SCH-Zulassung_1</t>
         </is>
       </c>
       <c r="C874" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -48797,11 +48797,11 @@
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_Ersatz</t>
+          <t>OB-SCH-Zulassung_1</t>
         </is>
       </c>
       <c r="C875" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -48853,11 +48853,11 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_Ersatz</t>
+          <t>OB-SCH-Zulassung_1</t>
         </is>
       </c>
       <c r="C876" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -48909,11 +48909,11 @@
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_KUN</t>
+          <t>OB-SCH-Zulassung_2</t>
         </is>
       </c>
       <c r="C877" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -48965,11 +48965,11 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_KUN</t>
+          <t>OB-SCH-Zulassung_2</t>
         </is>
       </c>
       <c r="C878" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -49021,11 +49021,11 @@
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_KUN</t>
+          <t>OB-SCH-Zulassung_2</t>
         </is>
       </c>
       <c r="C879" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -49077,11 +49077,11 @@
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_KUN</t>
+          <t>OB-SCH-Zulassung_2</t>
         </is>
       </c>
       <c r="C880" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -49133,15 +49133,15 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_KUN</t>
+          <t>OB-SCH-Zulassung_2</t>
         </is>
       </c>
       <c r="C881" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
-          <t>PSTVA5732</t>
+          <t>PSTVA5731</t>
         </is>
       </c>
       <c r="E881" t="inlineStr">
@@ -49189,15 +49189,15 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_KUN</t>
+          <t>OB-SCH-Zulassung_2</t>
         </is>
       </c>
       <c r="C882" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
-          <t>PSTVA5732</t>
+          <t>PSTVA5731</t>
         </is>
       </c>
       <c r="E882" t="inlineStr">
@@ -49245,11 +49245,11 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_KUV</t>
+          <t>OB-SCH-Zulassung_3</t>
         </is>
       </c>
       <c r="C883" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -49301,11 +49301,11 @@
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_KUV</t>
+          <t>OB-SCH-Zulassung_3</t>
         </is>
       </c>
       <c r="C884" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -49357,11 +49357,11 @@
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_KUV</t>
+          <t>OB-SCH-Zulassung_3</t>
         </is>
       </c>
       <c r="C885" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -49413,11 +49413,11 @@
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_KUV</t>
+          <t>OB-SCH-Zulassung_3</t>
         </is>
       </c>
       <c r="C886" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -49469,15 +49469,15 @@
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_KUV</t>
+          <t>OB-SCH-Zulassung_3</t>
         </is>
       </c>
       <c r="C887" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
-          <t>PSTVA5731</t>
+          <t>PSTVA5732</t>
         </is>
       </c>
       <c r="E887" t="inlineStr">
@@ -49525,15 +49525,15 @@
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_KUV</t>
+          <t>OB-SCH-Zulassung_3</t>
         </is>
       </c>
       <c r="C888" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
-          <t>PSTVA5731</t>
+          <t>PSTVA5732</t>
         </is>
       </c>
       <c r="E888" t="inlineStr">
@@ -49581,11 +49581,11 @@
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_MAM</t>
+          <t>OB-SCH-Zulassung_Ersatz</t>
         </is>
       </c>
       <c r="C889" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -49637,11 +49637,11 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_MAM</t>
+          <t>OB-SCH-Zulassung_Ersatz</t>
         </is>
       </c>
       <c r="C890" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -49693,11 +49693,11 @@
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_MAM</t>
+          <t>OB-SCH-Zulassung_Ersatz</t>
         </is>
       </c>
       <c r="C891" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -49749,11 +49749,11 @@
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_MAM</t>
+          <t>OB-SCH-Zulassung_Ersatz</t>
         </is>
       </c>
       <c r="C892" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -49805,11 +49805,11 @@
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_MAM</t>
+          <t>OB-SCH-Zulassung_Ersatz</t>
         </is>
       </c>
       <c r="C893" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -49861,11 +49861,11 @@
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>OB-SCH-Zulassung_MAM</t>
+          <t>OB-SCH-Zulassung_Ersatz</t>
         </is>
       </c>
       <c r="C894" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -70219,11 +70219,7 @@
           <t>Adressetikette</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>A4 -&gt; Match Page Size Landscape Manual Scaling 100% Origin at Center</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -70591,11 +70587,7 @@
           <t>Internationaler Führerausweis</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>A4 -&gt; CARi-DP-PCI 148 x 311 Landscape, Manual Scaling 100% Origin at Center</t>
-        </is>
-      </c>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -70664,11 +70656,7 @@
           <t>Versandetikette Fahrzeug</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>A4 -&gt; Match Page Size Landscape Manual Scaling 100% Origin at Center</t>
-        </is>
-      </c>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -70703,7 +70691,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Inspectdokument</t>
+          <t>Platzhalter für alle Inspect-Formulare</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
@@ -70718,7 +70706,7 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Drucker für automatischer Druck des LF</t>
+          <t>Platzhalter für Autoprint Lernfahrausweis</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
